--- a/report_forms/021_infection_control_monthly_compliance_report--report_forms.xlsx
+++ b/report_forms/021_infection_control_monthly_compliance_report--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -531,53 +531,53 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>reviewer</t>
+          <t>incident_description</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reviewer</t>
+          <t>Incident Description</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>facility</t>
+          <t>reviewer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Facility</t>
+          <t>Reviewer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,64 +589,64 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>incident_description</t>
+          <t>prevention_actions_taken</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Incident Description</t>
+          <t>Prevention Actions Taken</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>prevention_actions_taken</t>
+          <t>incident_status</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prevention Actions Taken</t>
+          <t>Incident Status</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>incident_status</t>
+          <t>follow_up_action</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Incident Status</t>
+          <t>Follow Up Action</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>follow_up_action</t>
+          <t>facility</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Follow Up Action</t>
+          <t>Facility</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reviewer Overseer</t>
+          <t>Reviewer's Name</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>incident_date</t>
+          <t>follow_up_action_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Incident Date</t>
+          <t>Follow Up Action 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reviewer_overseer</t>
+          <t>incident_status_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Reviewer Overseer</t>
+          <t>Incident Status 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>incident_description</t>
+          <t>prevention_actions_taken_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Incident Description</t>
+          <t>Actions Taken</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>prevention_actions_taken</t>
+          <t>facility_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prevention Actions Taken</t>
+          <t>Facility Name</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,269 +796,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>incident_status</t>
+          <t>reviewer_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Incident Status</t>
+          <t>Reviewer 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>follow_up_action</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Follow Up Action</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>facility</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>reviewer</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>incident_date</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Incident Date</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>facility</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>reviewer_overseer</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Reviewer Overseer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>incident_status</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Incident Status</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>follow_up_action</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Follow Up Action</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>incident_description</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Incident Description</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>prevention_actions_taken</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Prevention Actions Taken</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>reviewer</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1075,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1108,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1125,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1171,7 +918,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_status_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1188,7 +935,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>incident_status_choices</t>
+          <t>incident_status_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1205,102 +952,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>reviewer_choices</t>
+          <t>reviewer_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>reviewer_choices</t>
+          <t>reviewer_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>incident_status_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>incident_status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>inactive</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>reviewer_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>reviewer_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
